--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NORTH_CAROLINA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NORTH_CAROLINA_2014.xlsx
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C191">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C318">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C328">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C770">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C921">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C922">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C989">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C990">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C999">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1472">
@@ -30210,7 +30210,7 @@
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1659">
